--- a/upload/iniciativas_acordo_judicial_reparacao_vale.xlsx
+++ b/upload/iniciativas_acordo_judicial_reparacao_vale.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Desktop\Trabalho\AFPR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m1432701\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6030"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="9780"/>
   </bookViews>
   <sheets>
     <sheet name="in" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="87">
   <si>
     <t>Código Iniciativa </t>
   </si>
@@ -293,6 +293,12 @@
   </si>
   <si>
     <t>Melhoria da infraestrutura da Cidade Administrativa</t>
+  </si>
+  <si>
+    <t>Melhoria da infraestrutura dos municípios - Estruturação de Unidade do Corpo de Bombeiros de Minas Gerais em Brumadinho</t>
+  </si>
+  <si>
+    <t>Melhoria da infraestrutura dos municípios - Complementação de desapropriações, indenizações e despesas correlatas para implantação do Rodoanel da RMBH</t>
   </si>
 </sst>
 </file>
@@ -1135,7 +1141,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
@@ -2191,6 +2197,34 @@
       </c>
       <c r="D75" s="1">
         <v>40000000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>9521180</v>
+      </c>
+      <c r="B76" t="s">
+        <v>85</v>
+      </c>
+      <c r="C76" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76" s="1">
+        <v>3500000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>9521429</v>
+      </c>
+      <c r="B77" t="s">
+        <v>86</v>
+      </c>
+      <c r="C77" t="s">
+        <v>7</v>
+      </c>
+      <c r="D77" s="1">
+        <v>670000000</v>
       </c>
     </row>
   </sheetData>
